--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -779,7 +779,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sheet 'Monthly_GWh': GWh per month, ODS's own monthly production by technology (history before the daily data).</t>
+          <t>Sheet 'Monthly_GWh': GWh per month, ODS's own monthly production by technology (history before the daily data). It is ODS's 'Produccion General de Energia' table, which runs about 8-10% below gross generation (the same reports' 'Produccion Bruta' and the daily sheet are gross), so do not splice it onto the daily series unadjusted.</t>
         </is>
       </c>
     </row>
@@ -9678,15 +9678,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>Hydro_GWh</t>
@@ -10973,209 +10968,521 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>271.218</v>
+        <v>328.12</v>
       </c>
       <c r="C50" t="n">
-        <v>269.377</v>
+        <v>215.871</v>
       </c>
       <c r="D50" t="n">
-        <v>98.968</v>
+        <v>107.454</v>
       </c>
       <c r="E50" t="n">
-        <v>90.726</v>
+        <v>85.27800000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>37.912</v>
+        <v>34.806</v>
       </c>
       <c r="G50" t="n">
-        <v>20.028</v>
+        <v>20.548</v>
       </c>
       <c r="H50" t="n">
-        <v>788.23</v>
+        <v>792.076</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>248.362</v>
+        <v>261.203</v>
       </c>
       <c r="C51" t="n">
-        <v>235.797</v>
+        <v>264.515</v>
       </c>
       <c r="D51" t="n">
-        <v>84.295</v>
+        <v>85.56399999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>94.065</v>
+        <v>86.33</v>
       </c>
       <c r="F51" t="n">
-        <v>34.3</v>
+        <v>43.763</v>
       </c>
       <c r="G51" t="n">
-        <v>17.803</v>
+        <v>16.387</v>
       </c>
       <c r="H51" t="n">
-        <v>714.62</v>
+        <v>757.763</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>264.084</v>
+        <v>279.702</v>
       </c>
       <c r="C52" t="n">
-        <v>340.412</v>
+        <v>419.911</v>
       </c>
       <c r="D52" t="n">
-        <v>94.256</v>
+        <v>55.747</v>
       </c>
       <c r="E52" t="n">
-        <v>99.98699999999999</v>
+        <v>101.987</v>
       </c>
       <c r="F52" t="n">
-        <v>68.983</v>
+        <v>55.616</v>
       </c>
       <c r="G52" t="n">
-        <v>17.193</v>
+        <v>19.466</v>
       </c>
       <c r="H52" t="n">
-        <v>884.91</v>
+        <v>932.429</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>271.933</v>
+        <v>284.083</v>
       </c>
       <c r="C53" t="n">
-        <v>419.781</v>
+        <v>377.83</v>
       </c>
       <c r="D53" t="n">
-        <v>54.132</v>
+        <v>66.544</v>
       </c>
       <c r="E53" t="n">
-        <v>97.699</v>
+        <v>102.986</v>
       </c>
       <c r="F53" t="n">
-        <v>71.717</v>
+        <v>57.359</v>
       </c>
       <c r="G53" t="n">
-        <v>16.823</v>
+        <v>17.587</v>
       </c>
       <c r="H53" t="n">
-        <v>932.08</v>
+        <v>906.388</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>277.172</v>
+        <v>299.224</v>
       </c>
       <c r="C54" t="n">
-        <v>595.833</v>
+        <v>544.054</v>
       </c>
       <c r="D54" t="n">
-        <v>43.839</v>
+        <v>38.957</v>
       </c>
       <c r="E54" t="n">
-        <v>99.018</v>
+        <v>97.38800000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>73.14100000000001</v>
+        <v>59.948</v>
       </c>
       <c r="G54" t="n">
-        <v>16.669</v>
+        <v>18.414</v>
       </c>
       <c r="H54" t="n">
-        <v>1105.67</v>
+        <v>1057.986</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>46174</v>
+        <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>258.933</v>
+        <v>328.571</v>
       </c>
       <c r="C55" t="n">
-        <v>546.414</v>
+        <v>374.61</v>
       </c>
       <c r="D55" t="n">
-        <v>59.022</v>
+        <v>61.142</v>
       </c>
       <c r="E55" t="n">
-        <v>95.128</v>
+        <v>81.45</v>
       </c>
       <c r="F55" t="n">
-        <v>68.916</v>
+        <v>42.897</v>
       </c>
       <c r="G55" t="n">
-        <v>15.874</v>
+        <v>18.961</v>
       </c>
       <c r="H55" t="n">
-        <v>1044.29</v>
+        <v>907.631</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>46204</v>
+        <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>274.142</v>
+        <v>355.739</v>
       </c>
       <c r="C56" t="n">
-        <v>539.359</v>
+        <v>318.842</v>
       </c>
       <c r="D56" t="n">
-        <v>109.974</v>
+        <v>102.446</v>
       </c>
       <c r="E56" t="n">
-        <v>93.51300000000001</v>
+        <v>93.17400000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>60.656</v>
+        <v>46.692</v>
       </c>
       <c r="G56" t="n">
-        <v>17.03</v>
+        <v>18.886</v>
       </c>
       <c r="H56" t="n">
-        <v>1094.67</v>
+        <v>935.78</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B57" t="n">
+        <v>369.823</v>
+      </c>
+      <c r="C57" t="n">
+        <v>395.856</v>
+      </c>
+      <c r="D57" t="n">
+        <v>62.904</v>
+      </c>
+      <c r="E57" t="n">
+        <v>96.17700000000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>31.234</v>
+      </c>
+      <c r="G57" t="n">
+        <v>18.954</v>
+      </c>
+      <c r="H57" t="n">
+        <v>974.948</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B58" t="n">
+        <v>359.399</v>
+      </c>
+      <c r="C58" t="n">
+        <v>440.062</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30.331</v>
+      </c>
+      <c r="E58" t="n">
+        <v>88.374</v>
+      </c>
+      <c r="F58" t="n">
+        <v>20.761</v>
+      </c>
+      <c r="G58" t="n">
+        <v>18.521</v>
+      </c>
+      <c r="H58" t="n">
+        <v>957.448</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B59" t="n">
+        <v>421.349</v>
+      </c>
+      <c r="C59" t="n">
+        <v>324.768</v>
+      </c>
+      <c r="D59" t="n">
+        <v>34.136</v>
+      </c>
+      <c r="E59" t="n">
+        <v>82.947</v>
+      </c>
+      <c r="F59" t="n">
+        <v>36.275</v>
+      </c>
+      <c r="G59" t="n">
+        <v>19.409</v>
+      </c>
+      <c r="H59" t="n">
+        <v>918.885</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B60" t="n">
+        <v>349.478</v>
+      </c>
+      <c r="C60" t="n">
+        <v>236.858</v>
+      </c>
+      <c r="D60" t="n">
+        <v>94.482</v>
+      </c>
+      <c r="E60" t="n">
+        <v>81.158</v>
+      </c>
+      <c r="F60" t="n">
+        <v>35.064</v>
+      </c>
+      <c r="G60" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="H60" t="n">
+        <v>815.96</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B61" t="n">
+        <v>268.886</v>
+      </c>
+      <c r="C61" t="n">
+        <v>340.457</v>
+      </c>
+      <c r="D61" t="n">
+        <v>92.16200000000001</v>
+      </c>
+      <c r="E61" t="n">
+        <v>87.825</v>
+      </c>
+      <c r="F61" t="n">
+        <v>52.451</v>
+      </c>
+      <c r="G61" t="n">
+        <v>19.434</v>
+      </c>
+      <c r="H61" t="n">
+        <v>861.215</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B62" t="n">
+        <v>271.218</v>
+      </c>
+      <c r="C62" t="n">
+        <v>269.377</v>
+      </c>
+      <c r="D62" t="n">
+        <v>98.968</v>
+      </c>
+      <c r="E62" t="n">
+        <v>90.726</v>
+      </c>
+      <c r="F62" t="n">
+        <v>37.912</v>
+      </c>
+      <c r="G62" t="n">
+        <v>20.028</v>
+      </c>
+      <c r="H62" t="n">
+        <v>788.23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B63" t="n">
+        <v>248.362</v>
+      </c>
+      <c r="C63" t="n">
+        <v>235.797</v>
+      </c>
+      <c r="D63" t="n">
+        <v>84.295</v>
+      </c>
+      <c r="E63" t="n">
+        <v>94.065</v>
+      </c>
+      <c r="F63" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G63" t="n">
+        <v>17.803</v>
+      </c>
+      <c r="H63" t="n">
+        <v>714.62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" t="n">
+        <v>264.084</v>
+      </c>
+      <c r="C64" t="n">
+        <v>340.412</v>
+      </c>
+      <c r="D64" t="n">
+        <v>94.256</v>
+      </c>
+      <c r="E64" t="n">
+        <v>99.98699999999999</v>
+      </c>
+      <c r="F64" t="n">
+        <v>68.983</v>
+      </c>
+      <c r="G64" t="n">
+        <v>17.193</v>
+      </c>
+      <c r="H64" t="n">
+        <v>884.91</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>271.933</v>
+      </c>
+      <c r="C65" t="n">
+        <v>419.781</v>
+      </c>
+      <c r="D65" t="n">
+        <v>54.132</v>
+      </c>
+      <c r="E65" t="n">
+        <v>97.699</v>
+      </c>
+      <c r="F65" t="n">
+        <v>71.717</v>
+      </c>
+      <c r="G65" t="n">
+        <v>16.823</v>
+      </c>
+      <c r="H65" t="n">
+        <v>932.08</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B66" t="n">
+        <v>277.172</v>
+      </c>
+      <c r="C66" t="n">
+        <v>595.833</v>
+      </c>
+      <c r="D66" t="n">
+        <v>43.839</v>
+      </c>
+      <c r="E66" t="n">
+        <v>99.018</v>
+      </c>
+      <c r="F66" t="n">
+        <v>73.14100000000001</v>
+      </c>
+      <c r="G66" t="n">
+        <v>16.669</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1105.67</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>258.933</v>
+      </c>
+      <c r="C67" t="n">
+        <v>546.414</v>
+      </c>
+      <c r="D67" t="n">
+        <v>59.022</v>
+      </c>
+      <c r="E67" t="n">
+        <v>95.128</v>
+      </c>
+      <c r="F67" t="n">
+        <v>68.916</v>
+      </c>
+      <c r="G67" t="n">
+        <v>15.874</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1044.29</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>274.142</v>
+      </c>
+      <c r="C68" t="n">
+        <v>539.359</v>
+      </c>
+      <c r="D68" t="n">
+        <v>109.974</v>
+      </c>
+      <c r="E68" t="n">
+        <v>93.51300000000001</v>
+      </c>
+      <c r="F68" t="n">
+        <v>60.656</v>
+      </c>
+      <c r="G68" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1094.67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
         <v>46235</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B69" t="n">
         <v>220.392</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C69" t="n">
         <v>614.117</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D69" t="n">
         <v>115.473</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E69" t="n">
         <v>102.339</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F69" t="n">
         <v>44.919</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G69" t="n">
         <v>16.347</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H69" t="n">
         <v>1113.59</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -381,6 +381,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -638,6 +650,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -21,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,7 +158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Honduras power generation by type (ODS) (to Sep/26)</a:t>
+              <a:t>Honduras power generation by type (ODS) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +216,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -244,12 +244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +272,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -300,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$5</f>
+              <f>'Chart'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -328,12 +328,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$5</f>
+              <f>'Chart'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +356,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$5</f>
+              <f>'Chart'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -388,7 +388,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -426,6 +426,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -657,7 +663,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -695,6 +701,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1089,6 +1101,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1103,6 +1116,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1131,6 +1145,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1205,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1254,7 +1269,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B2" t="n">
@@ -1280,7 +1295,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B3" t="n">
@@ -1306,7 +1321,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B4" t="n">
@@ -1332,7 +1347,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B5" t="n">
@@ -1355,6 +1370,32 @@
       </c>
       <c r="H5" t="n">
         <v>670.7928000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9.8444</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.8891</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.5443</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21.8762</v>
       </c>
     </row>
   </sheetData>
@@ -1413,7 +1454,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1436,7 +1477,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1459,7 +1500,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1482,7 +1523,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1505,7 +1546,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1528,7 +1569,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1551,7 +1592,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1574,7 +1615,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1597,7 +1638,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1620,7 +1661,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1643,7 +1684,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1666,7 +1707,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1689,7 +1730,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1712,7 +1753,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1735,7 +1776,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1758,7 +1799,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1781,7 +1822,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1804,7 +1845,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1827,7 +1868,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1850,7 +1891,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1873,7 +1914,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1896,7 +1937,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1919,7 +1960,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1942,7 +1983,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1965,7 +2006,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1988,7 +2029,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2011,7 +2052,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2034,7 +2075,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2057,7 +2098,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2080,7 +2121,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2103,7 +2144,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2126,7 +2167,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2149,7 +2190,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2172,7 +2213,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2195,7 +2236,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2218,7 +2259,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2241,7 +2282,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2264,7 +2305,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2287,7 +2328,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2310,7 +2351,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2333,7 +2374,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2356,7 +2397,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2379,7 +2420,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2402,7 +2443,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2425,7 +2466,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2448,7 +2489,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2471,7 +2512,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2494,7 +2535,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2517,7 +2558,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2540,7 +2581,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2563,7 +2604,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2586,7 +2627,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2609,7 +2650,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2632,7 +2673,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2655,7 +2696,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2678,7 +2719,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2701,7 +2742,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2724,7 +2765,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2747,7 +2788,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2770,7 +2811,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2793,7 +2834,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2816,7 +2857,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2839,7 +2880,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2862,7 +2903,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2885,7 +2926,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2908,7 +2949,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2931,7 +2972,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2954,7 +2995,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2988,7 +3029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7316,6 +7357,41 @@
       </c>
       <c r="K123" t="n">
         <v>37347.4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B124" t="n">
+        <v>9844.4</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>65</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3889.1</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2544.3</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>18956.2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2366.4</v>
+      </c>
+      <c r="J124" t="n">
+        <v>553.6</v>
+      </c>
+      <c r="K124" t="n">
+        <v>38219</v>
       </c>
     </row>
   </sheetData>
@@ -7329,7 +7405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11657,6 +11733,41 @@
       </c>
       <c r="K123" t="n">
         <v>8047.7</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B124" t="n">
+        <v>2319</v>
+      </c>
+      <c r="C124" t="n">
+        <v>65</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3889.1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>553.6</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2366.4</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2544.3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-745.2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>15490.8</v>
+      </c>
+      <c r="J124" t="n">
+        <v>3465.4</v>
+      </c>
+      <c r="K124" t="n">
+        <v>7525.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1101,7 +1102,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1116,7 +1116,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1145,7 +1144,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1269,7 +1267,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B2" t="n">
@@ -1295,7 +1293,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B3" t="n">
@@ -1321,7 +1319,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B4" t="n">
@@ -1347,7 +1345,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B5" t="n">
@@ -1373,7 +1371,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B6" t="n">
@@ -1454,7 +1452,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1477,7 +1475,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1500,7 +1498,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1523,7 +1521,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1546,7 +1544,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1569,7 +1567,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1592,7 +1590,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1615,7 +1613,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1638,7 +1636,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1661,7 +1659,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1684,7 +1682,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1707,7 +1705,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1730,7 +1728,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1753,7 +1751,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1776,7 +1774,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1799,7 +1797,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1822,7 +1820,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1845,7 +1843,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1868,7 +1866,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1891,7 +1889,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1914,7 +1912,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1937,7 +1935,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1960,7 +1958,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1983,7 +1981,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2006,7 +2004,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2029,7 +2027,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2052,7 +2050,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2075,7 +2073,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2098,7 +2096,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2121,7 +2119,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2144,7 +2142,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2167,7 +2165,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2190,7 +2188,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2213,7 +2211,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2236,7 +2234,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2259,7 +2257,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2282,7 +2280,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2305,7 +2303,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2328,7 +2326,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2351,7 +2349,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2374,7 +2372,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2397,7 +2395,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2420,7 +2418,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2443,7 +2441,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2466,7 +2464,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2489,7 +2487,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2512,7 +2510,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2535,7 +2533,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2558,7 +2556,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2581,7 +2579,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2604,7 +2602,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2627,7 +2625,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2650,7 +2648,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2673,7 +2671,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2696,7 +2694,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2719,7 +2717,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2742,7 +2740,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2765,7 +2763,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2788,7 +2786,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2811,7 +2809,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2834,7 +2832,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2857,7 +2855,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2880,7 +2878,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2903,7 +2901,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2926,7 +2924,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2949,7 +2947,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2972,7 +2970,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2995,7 +2993,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -159,7 +159,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Honduras power generation by type (ODS) (to Oct/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Honduras power generation by type (ODS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -189,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$6</f>
+              <f>'Chart'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$6</f>
+              <f>'Chart'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$6</f>
+              <f>'Chart'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +302,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$6</f>
+              <f>'Chart'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +330,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$6</f>
+              <f>'Chart'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +358,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$6</f>
+              <f>'Chart'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -462,6 +463,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Honduras monthly production by technology (ODS reports) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -511,7 +513,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="5E5E5E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -595,7 +597,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -623,7 +625,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="A0522D"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1218,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1280,10 +1282,10 @@
         <v>58.8756</v>
       </c>
       <c r="E2" t="n">
-        <v>96.06189999999999</v>
+        <v>96.06190000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>65.45999999999999</v>
+        <v>65.46000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1309,7 +1311,7 @@
         <v>88.8043</v>
       </c>
       <c r="F3" t="n">
-        <v>77.842</v>
+        <v>77.84200000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1341,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>686.3674999999999</v>
+        <v>686.3674999999998</v>
       </c>
     </row>
     <row r="5">
@@ -1355,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>61.1246</v>
+        <v>61.12459999999999</v>
       </c>
       <c r="E5" t="n">
         <v>98.4911</v>
@@ -1368,32 +1370,6 @@
       </c>
       <c r="H5" t="n">
         <v>670.7928000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B6" t="n">
-        <v>9.8444</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.8891</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.5443</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>21.8762</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,13 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -160,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Honduras power generation by type (ODS) (to Sep/26)</a:t>
+              <a:t>Honduras power generation by type (ODS) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -190,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -218,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -246,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -274,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -302,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$5</f>
+              <f>'Chart'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -330,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$5</f>
+              <f>'Chart'!$G$2:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -358,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$5</f>
+              <f>'Chart'!$H$2:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -464,7 +463,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Honduras monthly production by technology (ODS reports) (to Aug/26)</a:t>
+              <a:t>Honduras monthly production by technology (ODS reports) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -494,12 +493,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - History'!$A$2:$A$69</f>
+              <f>'Chart - History'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - History'!$B$2:$B$69</f>
+              <f>'Chart - History'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -522,12 +521,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - History'!$A$2:$A$69</f>
+              <f>'Chart - History'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - History'!$C$2:$C$69</f>
+              <f>'Chart - History'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -550,12 +549,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - History'!$A$2:$A$69</f>
+              <f>'Chart - History'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - History'!$D$2:$D$69</f>
+              <f>'Chart - History'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -578,12 +577,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - History'!$A$2:$A$69</f>
+              <f>'Chart - History'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - History'!$E$2:$E$69</f>
+              <f>'Chart - History'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -606,12 +605,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - History'!$A$2:$A$69</f>
+              <f>'Chart - History'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - History'!$F$2:$F$69</f>
+              <f>'Chart - History'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -634,12 +633,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - History'!$A$2:$A$69</f>
+              <f>'Chart - History'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - History'!$G$2:$G$69</f>
+              <f>'Chart - History'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -1104,6 +1103,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1118,6 +1118,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1146,6 +1147,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1220,7 +1222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1269,7 +1271,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B2" t="n">
@@ -1295,7 +1297,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B3" t="n">
@@ -1321,7 +1323,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B4" t="n">
@@ -1347,7 +1349,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B5" t="n">
@@ -1370,6 +1372,32 @@
       </c>
       <c r="H5" t="n">
         <v>670.7928000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>242.1138</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>33.0163</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90.0505</v>
+      </c>
+      <c r="F6" t="n">
+        <v>63.50600000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>482.6313</v>
       </c>
     </row>
   </sheetData>
@@ -1384,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1428,7 +1456,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1451,7 +1479,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1474,7 +1502,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1497,7 +1525,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1520,7 +1548,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1543,7 +1571,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1566,7 +1594,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1589,7 +1617,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1612,7 +1640,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1635,7 +1663,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1658,7 +1686,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1681,7 +1709,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1704,7 +1732,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1727,7 +1755,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1750,7 +1778,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1773,7 +1801,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1796,7 +1824,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1819,7 +1847,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1842,7 +1870,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1865,7 +1893,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1888,7 +1916,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1911,7 +1939,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1934,7 +1962,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1957,7 +1985,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1980,7 +2008,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2003,7 +2031,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2026,7 +2054,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2049,7 +2077,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2072,7 +2100,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2095,7 +2123,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2118,7 +2146,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2141,7 +2169,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2164,7 +2192,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2187,7 +2215,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2210,7 +2238,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2233,7 +2261,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2256,7 +2284,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2279,7 +2307,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2302,7 +2330,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2325,7 +2353,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2348,7 +2376,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2371,7 +2399,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2394,7 +2422,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2417,7 +2445,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2440,7 +2468,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2463,7 +2491,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2486,7 +2514,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2509,7 +2537,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2532,7 +2560,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2555,7 +2583,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2578,7 +2606,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2601,7 +2629,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2624,7 +2652,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2647,7 +2675,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2670,7 +2698,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2693,7 +2721,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2716,7 +2744,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2739,7 +2767,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2762,7 +2790,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2785,7 +2813,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2808,7 +2836,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2831,7 +2859,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2854,7 +2882,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2877,7 +2905,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2900,7 +2928,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2923,7 +2951,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2946,7 +2974,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2969,7 +2997,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2989,6 +3017,29 @@
       </c>
       <c r="G69" t="n">
         <v>16.347</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>239.184</v>
+      </c>
+      <c r="C70" t="n">
+        <v>604.3630000000001</v>
+      </c>
+      <c r="D70" t="n">
+        <v>61.201</v>
+      </c>
+      <c r="E70" t="n">
+        <v>94.02800000000001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>45.759</v>
+      </c>
+      <c r="G70" t="n">
+        <v>16.272</v>
       </c>
     </row>
   </sheetData>
@@ -3003,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7366,6 +7417,881 @@
       </c>
       <c r="K124" t="n">
         <v>38219</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B125" t="n">
+        <v>9900.1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1541.3</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2469.3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>20234.7</v>
+      </c>
+      <c r="I125" t="n">
+        <v>2341.3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>559.6</v>
+      </c>
+      <c r="K125" t="n">
+        <v>37176.9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B126" t="n">
+        <v>9454.6</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>219.9</v>
+      </c>
+      <c r="E126" t="n">
+        <v>3210.1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2552.3</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>18003</v>
+      </c>
+      <c r="I126" t="n">
+        <v>2366.7</v>
+      </c>
+      <c r="J126" t="n">
+        <v>565.9</v>
+      </c>
+      <c r="K126" t="n">
+        <v>36372.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B127" t="n">
+        <v>8943.6</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3077.2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2552.9</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>16221.2</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2354.9</v>
+      </c>
+      <c r="J127" t="n">
+        <v>566.8</v>
+      </c>
+      <c r="K127" t="n">
+        <v>33928.3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B128" t="n">
+        <v>9484.6</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="E128" t="n">
+        <v>4363.9</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2552.9</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>18376.3</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2349.9</v>
+      </c>
+      <c r="J128" t="n">
+        <v>564.3</v>
+      </c>
+      <c r="K128" t="n">
+        <v>37822.7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B129" t="n">
+        <v>9964.700000000001</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>4116.5</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2547.4</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>18258.6</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2298.2</v>
+      </c>
+      <c r="J129" t="n">
+        <v>576.9</v>
+      </c>
+      <c r="K129" t="n">
+        <v>37931.1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B130" t="n">
+        <v>9594.799999999999</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="E130" t="n">
+        <v>4370.3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2461.4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>15944.6</v>
+      </c>
+      <c r="I130" t="n">
+        <v>2344.2</v>
+      </c>
+      <c r="J130" t="n">
+        <v>568.1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>35657</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B131" t="n">
+        <v>8888.5</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3512.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1726.7</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>16693</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2355.5</v>
+      </c>
+      <c r="J131" t="n">
+        <v>574.9</v>
+      </c>
+      <c r="K131" t="n">
+        <v>33780.2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B132" t="n">
+        <v>9400</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3581.2</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1698</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>14682.8</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2345.6</v>
+      </c>
+      <c r="J132" t="n">
+        <v>565.6</v>
+      </c>
+      <c r="K132" t="n">
+        <v>32606.6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B133" t="n">
+        <v>8213.799999999999</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1659.5</v>
+      </c>
+      <c r="E133" t="n">
+        <v>4136.2</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1850.1</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>14643.8</v>
+      </c>
+      <c r="I133" t="n">
+        <v>2337.8</v>
+      </c>
+      <c r="J133" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="K133" t="n">
+        <v>33395.7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B134" t="n">
+        <v>8751.799999999999</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2617.6</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1894.9</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2552.6</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>13527.5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2300.1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>574</v>
+      </c>
+      <c r="K134" t="n">
+        <v>32218.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B135" t="n">
+        <v>9322.4</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2413.9</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3873.4</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2548.9</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>16029.2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>2250.1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>558.3</v>
+      </c>
+      <c r="K135" t="n">
+        <v>36996.2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B136" t="n">
+        <v>9766.799999999999</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1125.3</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4044</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2551</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>17053.2</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2299.1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>564.3</v>
+      </c>
+      <c r="K136" t="n">
+        <v>37403.7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B137" t="n">
+        <v>10194.2</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1386.1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3557.1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2536.9</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>17249.1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>2340.7</v>
+      </c>
+      <c r="J137" t="n">
+        <v>538.8</v>
+      </c>
+      <c r="K137" t="n">
+        <v>37802.9</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B138" t="n">
+        <v>9439.700000000001</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1321.7</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3409.2</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2547.9</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>18131.5</v>
+      </c>
+      <c r="I138" t="n">
+        <v>2361.1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>547.8</v>
+      </c>
+      <c r="K138" t="n">
+        <v>37758.9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B139" t="n">
+        <v>10107.1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3170.2</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2553.7</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>17749.5</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2234.3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>551.7</v>
+      </c>
+      <c r="K139" t="n">
+        <v>36756.7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8220.200000000001</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2362.7</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2551.7</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>18098</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2167.9</v>
+      </c>
+      <c r="J140" t="n">
+        <v>577.9</v>
+      </c>
+      <c r="K140" t="n">
+        <v>34333.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B141" t="n">
+        <v>8916.700000000001</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>996.5</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2914.9</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2553.3</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>13392.7</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2282.7</v>
+      </c>
+      <c r="J141" t="n">
+        <v>573</v>
+      </c>
+      <c r="K141" t="n">
+        <v>31629.8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B142" t="n">
+        <v>9601.200000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1294.4</v>
+      </c>
+      <c r="E142" t="n">
+        <v>3344.3</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2549.6</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>16440.5</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1946.2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>571.1</v>
+      </c>
+      <c r="K142" t="n">
+        <v>35747.3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B143" t="n">
+        <v>9660.9</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1808.5</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3468.2</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2548.8</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>16687.4</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1656.5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>550.7</v>
+      </c>
+      <c r="K143" t="n">
+        <v>36381</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B144" t="n">
+        <v>10490.3</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1590.3</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3559.3</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2552.9</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>16778.4</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1508.6</v>
+      </c>
+      <c r="J144" t="n">
+        <v>558.5</v>
+      </c>
+      <c r="K144" t="n">
+        <v>37038.3</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8704.799999999999</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1486.2</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3353.9</v>
+      </c>
+      <c r="F145" t="n">
+        <v>2549.6</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>18081.9</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1513.2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="K145" t="n">
+        <v>36243.8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B146" t="n">
+        <v>9249</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2609.2</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3128.8</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2553.9</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>13630</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1524.1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>593.4</v>
+      </c>
+      <c r="K146" t="n">
+        <v>33288.4</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B147" t="n">
+        <v>9180.1</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3535.3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>4033.7</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2568.1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>9564.5</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1724.5</v>
+      </c>
+      <c r="J147" t="n">
+        <v>607.1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>31213.3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B148" t="n">
+        <v>8082</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3650.7</v>
+      </c>
+      <c r="E148" t="n">
+        <v>3909.5</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2551</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>7524.8</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1959.1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>602.1</v>
+      </c>
+      <c r="K148" t="n">
+        <v>28279.2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B149" t="n">
+        <v>8737.5</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3113.3</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4227.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2280.8</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>10513.1</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1869.2</v>
+      </c>
+      <c r="J149" t="n">
+        <v>594.8</v>
+      </c>
+      <c r="K149" t="n">
+        <v>31336.4</v>
       </c>
     </row>
   </sheetData>
@@ -7379,7 +8305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11742,6 +12668,881 @@
       </c>
       <c r="K124" t="n">
         <v>7525.4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B125" t="n">
+        <v>2214</v>
+      </c>
+      <c r="C125" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1541.3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>559.6</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2341.3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2469.3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-675.8</v>
+      </c>
+      <c r="I125" t="n">
+        <v>16363.1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>3871.6</v>
+      </c>
+      <c r="K125" t="n">
+        <v>7686.1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B126" t="n">
+        <v>2068.1</v>
+      </c>
+      <c r="C126" t="n">
+        <v>219.9</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3210.1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>565.9</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2366.7</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2552.3</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-419.5</v>
+      </c>
+      <c r="I126" t="n">
+        <v>15694.8</v>
+      </c>
+      <c r="J126" t="n">
+        <v>2308.2</v>
+      </c>
+      <c r="K126" t="n">
+        <v>7386.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B127" t="n">
+        <v>2726.7</v>
+      </c>
+      <c r="C127" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3077.2</v>
+      </c>
+      <c r="E127" t="n">
+        <v>566.8</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2354.9</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2552.9</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-608.5</v>
+      </c>
+      <c r="I127" t="n">
+        <v>13818</v>
+      </c>
+      <c r="J127" t="n">
+        <v>2403.2</v>
+      </c>
+      <c r="K127" t="n">
+        <v>6216.9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B128" t="n">
+        <v>2655.5</v>
+      </c>
+      <c r="C128" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4363.9</v>
+      </c>
+      <c r="E128" t="n">
+        <v>564.3</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2349.9</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2552.9</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-191.8</v>
+      </c>
+      <c r="I128" t="n">
+        <v>15574.9</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2801.4</v>
+      </c>
+      <c r="K128" t="n">
+        <v>6829.1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B129" t="n">
+        <v>2667.7</v>
+      </c>
+      <c r="C129" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4116.5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>576.9</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2298.2</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2547.4</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-610.5</v>
+      </c>
+      <c r="I129" t="n">
+        <v>15831.4</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2427.2</v>
+      </c>
+      <c r="K129" t="n">
+        <v>7297</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B130" t="n">
+        <v>2636.3</v>
+      </c>
+      <c r="C130" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="D130" t="n">
+        <v>4370.3</v>
+      </c>
+      <c r="E130" t="n">
+        <v>568.1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2344.2</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2461.4</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-421</v>
+      </c>
+      <c r="I130" t="n">
+        <v>13801.4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2143.2</v>
+      </c>
+      <c r="K130" t="n">
+        <v>6958.5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B131" t="n">
+        <v>2624.1</v>
+      </c>
+      <c r="C131" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3512.9</v>
+      </c>
+      <c r="E131" t="n">
+        <v>574.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2355.5</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1726.7</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-307.4</v>
+      </c>
+      <c r="I131" t="n">
+        <v>13459.9</v>
+      </c>
+      <c r="J131" t="n">
+        <v>3233.1</v>
+      </c>
+      <c r="K131" t="n">
+        <v>6264.4</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2714</v>
+      </c>
+      <c r="C132" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3581.2</v>
+      </c>
+      <c r="E132" t="n">
+        <v>565.6</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2345.6</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1698</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-194.9</v>
+      </c>
+      <c r="I132" t="n">
+        <v>13398.2</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1284.6</v>
+      </c>
+      <c r="K132" t="n">
+        <v>6686</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B133" t="n">
+        <v>2685.7</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1659.5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>4136.2</v>
+      </c>
+      <c r="E133" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2337.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1850.1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-182.9</v>
+      </c>
+      <c r="I133" t="n">
+        <v>13527.5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1116.3</v>
+      </c>
+      <c r="K133" t="n">
+        <v>5528.1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B134" t="n">
+        <v>2618.3</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2617.6</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1894.9</v>
+      </c>
+      <c r="E134" t="n">
+        <v>574</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2300.1</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2552.6</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-266.5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>13064.1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>463.4</v>
+      </c>
+      <c r="K134" t="n">
+        <v>6133.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B135" t="n">
+        <v>2624.8</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2413.9</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3873.4</v>
+      </c>
+      <c r="E135" t="n">
+        <v>558.3</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2250.1</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2548.9</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-247.8</v>
+      </c>
+      <c r="I135" t="n">
+        <v>13948.2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2081</v>
+      </c>
+      <c r="K135" t="n">
+        <v>6697.6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B136" t="n">
+        <v>2514.4</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1125.3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>4044</v>
+      </c>
+      <c r="E136" t="n">
+        <v>564.3</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2299.1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2551</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-310</v>
+      </c>
+      <c r="I136" t="n">
+        <v>14635.9</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2417.3</v>
+      </c>
+      <c r="K136" t="n">
+        <v>7252.4</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B137" t="n">
+        <v>2556.6</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1386.1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3557.1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>538.8</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2340.7</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2536.9</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-290.7</v>
+      </c>
+      <c r="I137" t="n">
+        <v>14454.7</v>
+      </c>
+      <c r="J137" t="n">
+        <v>2794.4</v>
+      </c>
+      <c r="K137" t="n">
+        <v>7637.6</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2313.9</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1321.7</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3409.2</v>
+      </c>
+      <c r="E138" t="n">
+        <v>547.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2361.1</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2547.9</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-430.1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>14755.7</v>
+      </c>
+      <c r="J138" t="n">
+        <v>3375.8</v>
+      </c>
+      <c r="K138" t="n">
+        <v>7125.8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2474.3</v>
+      </c>
+      <c r="C139" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3170.2</v>
+      </c>
+      <c r="E139" t="n">
+        <v>551.7</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2234.3</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2553.7</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-305.5</v>
+      </c>
+      <c r="I139" t="n">
+        <v>15065.2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2684.3</v>
+      </c>
+      <c r="K139" t="n">
+        <v>7632.8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B140" t="n">
+        <v>2776.2</v>
+      </c>
+      <c r="C140" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2362.7</v>
+      </c>
+      <c r="E140" t="n">
+        <v>577.9</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2167.9</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2551.7</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-523.2</v>
+      </c>
+      <c r="I140" t="n">
+        <v>17727.1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5444</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2783.6</v>
+      </c>
+      <c r="C141" t="n">
+        <v>996.5</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2914.9</v>
+      </c>
+      <c r="E141" t="n">
+        <v>573</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2282.7</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2553.3</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-810.2</v>
+      </c>
+      <c r="I141" t="n">
+        <v>13381.9</v>
+      </c>
+      <c r="J141" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K141" t="n">
+        <v>6133.1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2893.3</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1294.4</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3344.3</v>
+      </c>
+      <c r="E142" t="n">
+        <v>571.1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1946.2</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2549.6</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-608.2</v>
+      </c>
+      <c r="I142" t="n">
+        <v>16059.2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="K142" t="n">
+        <v>6707.9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2735.3</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1808.5</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3468.2</v>
+      </c>
+      <c r="E143" t="n">
+        <v>550.7</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1656.5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2548.8</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-1087.3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>15870.2</v>
+      </c>
+      <c r="J143" t="n">
+        <v>817.2</v>
+      </c>
+      <c r="K143" t="n">
+        <v>6925.6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2803.6</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1590.3</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3559.3</v>
+      </c>
+      <c r="E144" t="n">
+        <v>558.5</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1508.6</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2552.9</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-863.5</v>
+      </c>
+      <c r="I144" t="n">
+        <v>15928.2</v>
+      </c>
+      <c r="J144" t="n">
+        <v>850.2</v>
+      </c>
+      <c r="K144" t="n">
+        <v>7686.7</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B145" t="n">
+        <v>2497.4</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1486.2</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3353.9</v>
+      </c>
+      <c r="E145" t="n">
+        <v>554.2</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1513.2</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2549.6</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-503.8</v>
+      </c>
+      <c r="I145" t="n">
+        <v>17140.1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>941.8</v>
+      </c>
+      <c r="K145" t="n">
+        <v>6207.4</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2917.8</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2609.2</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3128.8</v>
+      </c>
+      <c r="E146" t="n">
+        <v>593.4</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1524.1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2553.9</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-194.5</v>
+      </c>
+      <c r="I146" t="n">
+        <v>13503.7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="K146" t="n">
+        <v>6331.2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2917.5</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3535.3</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4033.7</v>
+      </c>
+      <c r="E147" t="n">
+        <v>607.1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1724.5</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2568.1</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-1402.2</v>
+      </c>
+      <c r="I147" t="n">
+        <v>9512.700000000001</v>
+      </c>
+      <c r="J147" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="K147" t="n">
+        <v>6262.6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2839.7</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3650.7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3909.5</v>
+      </c>
+      <c r="E148" t="n">
+        <v>602.1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1959.1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2551</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-1646.2</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7216.2</v>
+      </c>
+      <c r="J148" t="n">
+        <v>308.6</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5242.3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2671.6</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3113.3</v>
+      </c>
+      <c r="D149" t="n">
+        <v>4227.7</v>
+      </c>
+      <c r="E149" t="n">
+        <v>594.8</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1869.2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2280.8</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-897.3</v>
+      </c>
+      <c r="I149" t="n">
+        <v>10383.2</v>
+      </c>
+      <c r="J149" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="K149" t="n">
+        <v>6065.9</v>
       </c>
     </row>
   </sheetData>
@@ -11755,7 +13556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13568,6 +15369,32 @@
         <v>1113.59</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>239.184</v>
+      </c>
+      <c r="C70" t="n">
+        <v>604.3630000000001</v>
+      </c>
+      <c r="D70" t="n">
+        <v>61.201</v>
+      </c>
+      <c r="E70" t="n">
+        <v>94.02800000000001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>45.759</v>
+      </c>
+      <c r="G70" t="n">
+        <v>16.272</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1060.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -1379,25 +1379,25 @@
         <v>46296</v>
       </c>
       <c r="B6" t="n">
-        <v>242.1138</v>
+        <v>250.9846</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>33.0163</v>
+        <v>34.3704</v>
       </c>
       <c r="E6" t="n">
-        <v>90.0505</v>
+        <v>94.6357</v>
       </c>
       <c r="F6" t="n">
-        <v>63.50600000000001</v>
+        <v>66.05719999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>482.6313</v>
+        <v>497.967</v>
       </c>
     </row>
   </sheetData>
@@ -3054,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8292,6 +8292,41 @@
       </c>
       <c r="K149" t="n">
         <v>31336.4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B150" t="n">
+        <v>8870.799999999999</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1354.1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>4585.2</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2551.2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>13818.2</v>
+      </c>
+      <c r="I150" t="n">
+        <v>915.1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>602.4</v>
+      </c>
+      <c r="K150" t="n">
+        <v>32697</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +8340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13543,6 +13578,41 @@
       </c>
       <c r="K149" t="n">
         <v>6065.9</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B150" t="n">
+        <v>2468.3</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1354.1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>4585.2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>602.4</v>
+      </c>
+      <c r="F150" t="n">
+        <v>915.1</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2551.2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-736.5</v>
+      </c>
+      <c r="I150" t="n">
+        <v>13770.6</v>
+      </c>
+      <c r="J150" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="K150" t="n">
+        <v>6402.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -1379,25 +1379,25 @@
         <v>46296</v>
       </c>
       <c r="B6" t="n">
-        <v>250.9846</v>
+        <v>260.2666</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3704</v>
+        <v>36.3531</v>
       </c>
       <c r="E6" t="n">
-        <v>94.6357</v>
+        <v>98.5424</v>
       </c>
       <c r="F6" t="n">
-        <v>66.05719999999999</v>
+        <v>68.61199999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>497.967</v>
+        <v>513.3741</v>
       </c>
     </row>
   </sheetData>
@@ -3054,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8327,6 +8327,41 @@
       </c>
       <c r="K150" t="n">
         <v>32697</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B151" t="n">
+        <v>9282</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1982.7</v>
+      </c>
+      <c r="E151" t="n">
+        <v>3906.7</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2554.8</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>13885.4</v>
+      </c>
+      <c r="I151" t="n">
+        <v>913.8</v>
+      </c>
+      <c r="J151" t="n">
+        <v>607.9</v>
+      </c>
+      <c r="K151" t="n">
+        <v>33133.3</v>
       </c>
     </row>
   </sheetData>
@@ -8340,7 +8375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13613,6 +13648,41 @@
       </c>
       <c r="K150" t="n">
         <v>6402.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B151" t="n">
+        <v>2418.8</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1982.7</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3906.7</v>
+      </c>
+      <c r="E151" t="n">
+        <v>607.9</v>
+      </c>
+      <c r="F151" t="n">
+        <v>913.8</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2554.8</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-826.2</v>
+      </c>
+      <c r="I151" t="n">
+        <v>13808.4</v>
+      </c>
+      <c r="J151" t="n">
+        <v>77</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6863.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/honduras_power_generation_daily.xlsx
@@ -1379,25 +1379,25 @@
         <v>46296</v>
       </c>
       <c r="B6" t="n">
-        <v>260.2666</v>
+        <v>269.4266</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>36.3531</v>
+        <v>37.9971</v>
       </c>
       <c r="E6" t="n">
-        <v>98.5424</v>
+        <v>102.5016</v>
       </c>
       <c r="F6" t="n">
-        <v>68.61199999999999</v>
+        <v>71.1579</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>513.3741</v>
+        <v>529.6320000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3054,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8362,6 +8362,41 @@
       </c>
       <c r="K151" t="n">
         <v>33133.3</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B152" t="n">
+        <v>9160</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1644</v>
+      </c>
+      <c r="E152" t="n">
+        <v>3959.2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>2545.9</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>14737.6</v>
+      </c>
+      <c r="I152" t="n">
+        <v>908.4</v>
+      </c>
+      <c r="J152" t="n">
+        <v>611.9</v>
+      </c>
+      <c r="K152" t="n">
+        <v>33567</v>
       </c>
     </row>
   </sheetData>
@@ -8375,7 +8410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13683,6 +13718,41 @@
       </c>
       <c r="K151" t="n">
         <v>6863.2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2359.7</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1644</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3959.2</v>
+      </c>
+      <c r="E152" t="n">
+        <v>611.9</v>
+      </c>
+      <c r="F152" t="n">
+        <v>908.4</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2545.9</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-820.7</v>
+      </c>
+      <c r="I152" t="n">
+        <v>14681.7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="K152" t="n">
+        <v>6800.3</v>
       </c>
     </row>
   </sheetData>
